--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487687_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487687_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6587</v>
+        <v>2.7583</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0638</v>
+        <v>2.8636</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4051</v>
+        <v>-0.1053</v>
       </c>
       <c r="G2" t="n">
         <v>2.9235</v>
@@ -610,13 +610,13 @@
         <v>0.9702</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7337</v>
+        <v>0.8333</v>
       </c>
       <c r="T2" t="n">
-        <v>0.729</v>
+        <v>0.5288</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0047</v>
+        <v>0.3045</v>
       </c>
       <c r="V2" t="n">
         <v>0.9418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4005</v>
+        <v>1.6814</v>
       </c>
       <c r="E3" t="n">
-        <v>1.883</v>
+        <v>1.0822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5175</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>1.7993</v>
@@ -688,13 +688,13 @@
         <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2012</v>
+        <v>1.4822</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7003</v>
+        <v>0.8995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5009</v>
+        <v>0.5827</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0478</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6334</v>
+        <v>1.1334</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6737</v>
+        <v>1.4735</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0403</v>
+        <v>-0.3401</v>
       </c>
       <c r="G4" t="n">
         <v>0.8045</v>
@@ -766,13 +766,13 @@
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5752</v>
+        <v>0.0752</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1233</v>
+        <v>-0.0769</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4518</v>
+        <v>0.152</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.322</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7761</v>
+        <v>0.5253</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7674</v>
+        <v>-0.2033</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4051</v>
+        <v>-1.8731</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5347</v>
+        <v>-1.5316</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9398</v>
+        <v>-0.3415</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.655</v>
+        <v>-1.1258</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6797</v>
+        <v>-0.5396</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3347</v>
+        <v>-0.5861</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2498</v>
+        <v>-0.7473</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.145</v>
+        <v>-0.992</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3948</v>
+        <v>0.2447</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1274</v>
+        <v>0.8339</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1211</v>
+        <v>0.6079</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0063</v>
+        <v>0.226</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3299</v>
+        <v>3.1075</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.9537</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3299</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0285</v>
+        <v>0.2822</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1826</v>
+        <v>-0.676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1541</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9015</v>
+        <v>-0.4051</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0183</v>
+        <v>0.5347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1168</v>
+        <v>-0.9398</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3048</v>
+        <v>-0.655</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3048</v>
+        <v>0.6797</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.3347</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5967</v>
+        <v>0.2498</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7135</v>
+        <v>-0.145</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1168</v>
+        <v>0.3948</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0969</v>
+        <v>0.1635</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1222</v>
+        <v>-0.021</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0253</v>
+        <v>0.1845</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0323</v>
+        <v>-0.3744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5253</v>
+        <v>-0.583</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5576</v>
+        <v>0.2086</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8731</v>
+        <v>-0.9015</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5316</v>
+        <v>-1.0183</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3415</v>
+        <v>0.1168</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1258</v>
+        <v>-0.3048</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5396</v>
+        <v>-0.3048</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5861</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7473</v>
+        <v>-0.5967</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.992</v>
+        <v>-0.7135</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2447</v>
+        <v>0.1168</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4796</v>
+        <v>-0.249</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6079</v>
+        <v>-0.2782</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1283</v>
+        <v>0.0292</v>
       </c>
       <c r="V7" t="n">
-        <v>3.1075</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.9537</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. MORENO ABAD</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4904</v>
+        <v>-1.1825</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0606</v>
+        <v>-2.0111</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4298</v>
+        <v>0.8287</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.206</v>
+        <v>-1.4158</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.206</v>
+        <v>-1.7005</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.2847</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.7123</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.7579</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.206</v>
+        <v>-0.7034</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.206</v>
+        <v>-0.9425</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2391</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0606</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0606</v>
+        <v>0.3594</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.3679</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>G. MORENO ABAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8376</v>
+        <v>-1.4904</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6117</v>
+        <v>-0.0606</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7741</v>
+        <v>-1.4298</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4158</v>
+        <v>-0.206</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7005</v>
+        <v>-0.206</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2847</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7123</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7579</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7034</v>
+        <v>-0.206</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9425</v>
+        <v>-0.206</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2391</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0722</v>
+        <v>-0.0606</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2412</v>
+        <v>-0.0606</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3134</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.263</v>
+        <v>-2.3448</v>
       </c>
       <c r="E10" t="n">
         <v>-1.4709</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7922</v>
+        <v>-0.8739</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5616</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2001</v>
+        <v>0.1183</v>
       </c>
       <c r="T10" t="n">
         <v>0.1828</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0173</v>
+        <v>-0.0645</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3194</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0287</v>
+        <v>-3.0099</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.242</v>
+        <v>-3.4027</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2134</v>
+        <v>0.3928</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8156</v>
+        <v>-1.4641</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.671</v>
+        <v>-2.3933</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1446</v>
+        <v>0.9292</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.969</v>
+        <v>-1.2336</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.969</v>
+        <v>-1.9237</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.6901</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8466</v>
+        <v>-0.2305</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7019</v>
+        <v>-0.4696</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1446</v>
+        <v>0.2391</v>
       </c>
       <c r="P11" t="n">
         <v>-0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>0.981</v>
+        <v>0.2602</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3028</v>
+        <v>-0.2288</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2838</v>
+        <v>0.489</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7561</v>
+        <v>-3.5282</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2035</v>
+        <v>-3.1419</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4474</v>
+        <v>-0.3862</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4641</v>
+        <v>-2.8156</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3933</v>
+        <v>-2.671</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9292</v>
+        <v>-0.1446</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2336</v>
+        <v>-1.969</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9237</v>
+        <v>-1.969</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6901</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2305</v>
+        <v>-0.8466</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4696</v>
+        <v>-0.7019</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2391</v>
+        <v>-0.1446</v>
       </c>
       <c r="P12" t="n">
         <v>-0.5821</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4861</v>
+        <v>0.4814</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0296</v>
+        <v>-0.2027</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5436</v>
+        <v>0.6842</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.752699999999999</v>
+        <v>-5.7529</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.401600000000001</v>
+        <v>-5.4016</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3511</v>
+        <v>-0.3509999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>-4.115499999999999</v>
@@ -1441,16 +1441,16 @@
         <v>1.2233</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0229</v>
+        <v>2.022899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9116</v>
+        <v>1.911600000000001</v>
       </c>
       <c r="L13" t="n">
         <v>0.1114000000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.1383</v>
+        <v>-6.138300000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-7.2502</v>
@@ -1468,13 +1468,13 @@
         <v>9.701599999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>4.665799999999999</v>
+        <v>4.6657</v>
       </c>
       <c r="T13" t="n">
         <v>1.7102</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9556</v>
+        <v>2.9555</v>
       </c>
       <c r="V13" t="n">
         <v>1.4583</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9155</v>
+        <v>7.6697</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0803</v>
+        <v>5.78</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8351</v>
+        <v>1.8896</v>
       </c>
       <c r="G14" t="n">
         <v>5.6078</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5088</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1189</v>
+        <v>-0.4192</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3898</v>
+        <v>-0.3353</v>
       </c>
       <c r="V14" t="n">
         <v>1.4582</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1905</v>
+        <v>7.5904</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0836</v>
+        <v>5.1837</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1069</v>
+        <v>2.4067</v>
       </c>
       <c r="G15" t="n">
         <v>3.131</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1943</v>
+        <v>-0.7944</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3623</v>
+        <v>-0.2622</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.832</v>
+        <v>-0.5322</v>
       </c>
       <c r="V15" t="n">
         <v>4.2836</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7631</v>
+        <v>1.7621</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6975</v>
+        <v>-1.6985</v>
       </c>
       <c r="F16" t="n">
         <v>3.4607</v>
@@ -1702,10 +1702,10 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5832000000000001</v>
+        <v>-0.4178</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9118000000000001</v>
+        <v>-0.0892</v>
       </c>
       <c r="U16" t="n">
         <v>-0.3286</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3575</v>
+        <v>0.3847</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4344</v>
+        <v>0.034</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9231</v>
+        <v>0.3507</v>
       </c>
       <c r="G17" t="n">
         <v>1.3133</v>
@@ -1780,13 +1780,13 @@
         <v>2.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7158</v>
+        <v>0.743</v>
       </c>
       <c r="T17" t="n">
-        <v>0.609</v>
+        <v>0.2086</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1068</v>
+        <v>0.5345</v>
       </c>
       <c r="V17" t="n">
         <v>-2.4477</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6391</v>
+        <v>0.3299</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6362</v>
+        <v>-0.8364</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2754</v>
+        <v>1.1664</v>
       </c>
       <c r="G18" t="n">
         <v>2.0568</v>
@@ -1858,13 +1858,13 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5823</v>
+        <v>0.2731</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.12</v>
+        <v>-0.3202</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7023</v>
+        <v>0.5933</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8931</v>
+        <v>-3.3151</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5919</v>
+        <v>-3.0626</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3012</v>
+        <v>-0.2526</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8633</v>
+        <v>-2.0542</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2933</v>
+        <v>1.7285</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.57</v>
+        <v>-3.7827</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3306</v>
+        <v>-1.4782</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4779</v>
+        <v>1.6148</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1473</v>
+        <v>-3.0931</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1939</v>
+        <v>-0.5759</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7712</v>
+        <v>0.1137</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4227</v>
+        <v>-0.6896</v>
       </c>
       <c r="P19" t="n">
         <v>0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7463</v>
+        <v>2.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9224</v>
+        <v>-1.4729</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5747</v>
+        <v>-0.6738</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3477</v>
+        <v>-0.7991</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8836</v>
+        <v>-0.5642</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3776</v>
+        <v>1.2239</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.506</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5158</v>
+        <v>-3.3287</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9634</v>
+        <v>-1.8912</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5524</v>
+        <v>-1.4374</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0542</v>
+        <v>-0.8633</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7285</v>
+        <v>-0.2933</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.7827</v>
+        <v>-0.57</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4782</v>
+        <v>0.3306</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6148</v>
+        <v>0.4779</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.0931</v>
+        <v>-0.1473</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5759</v>
+        <v>-1.1939</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1137</v>
+        <v>-0.7712</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6896</v>
+        <v>-0.4227</v>
       </c>
       <c r="P20" t="n">
         <v>0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9105</v>
+        <v>1.7463</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6736</v>
+        <v>-1.3579</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5747</v>
+        <v>-0.874</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0989</v>
+        <v>-0.4839</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5642</v>
+        <v>-1.8836</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2239</v>
+        <v>-0.3776</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.788</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7041</v>
+        <v>-5.3403</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.358</v>
+        <v>-3.1578</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.346</v>
+        <v>-2.1825</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9485</v>
@@ -2092,13 +2092,13 @@
         <v>2.1344</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2481</v>
+        <v>-0.8844</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7257</v>
+        <v>-0.5255</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5224</v>
+        <v>-0.3589</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4477</v>
@@ -2128,10 +2128,10 @@
         <v>5.752699999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3513000000000002</v>
+        <v>0.3511999999999986</v>
       </c>
       <c r="F22" t="n">
-        <v>5.401600000000001</v>
+        <v>5.401599999999999</v>
       </c>
       <c r="G22" t="n">
         <v>4.1153</v>
@@ -2143,7 +2143,7 @@
         <v>-1.2234</v>
       </c>
       <c r="J22" t="n">
-        <v>6.1385</v>
+        <v>6.138500000000001</v>
       </c>
       <c r="K22" t="n">
         <v>7.250299999999999</v>
@@ -2170,13 +2170,13 @@
         <v>17.4631</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.665900000000001</v>
+        <v>-4.665800000000001</v>
       </c>
       <c r="T22" t="n">
         <v>-2.9555</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7103</v>
+        <v>-1.7102</v>
       </c>
       <c r="V22" t="n">
         <v>-1.458100000000002</v>
